--- a/Lab5/uP16_Assembler.xlsx
+++ b/Lab5/uP16_Assembler.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asdouglas\Work\Xilinx\labs\2003\newLab5\__student files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SC2103-Lab-main\Lab5_temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD9EFF6-E999-46F2-B707-4E06A4017B0C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC791E9-E9FD-401F-8D5B-5E57F0FD5251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="285" yWindow="885" windowWidth="21990" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="45" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base Code" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -92,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="47">
   <si>
     <t>nop</t>
   </si>
@@ -229,13 +232,10 @@
     <t>f9</t>
   </si>
   <si>
-    <t>3c</t>
-  </si>
-  <si>
     <t>e1</t>
   </si>
   <si>
-    <t>dd</t>
+    <t>DD</t>
   </si>
 </sst>
 </file>
@@ -2465,28 +2465,22 @@
       </c>
       <c r="I34" s="23"/>
       <c r="J34" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="K34" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="L34" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="M34" s="35">
-        <v>9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K34" s="34"/>
+      <c r="L34" s="34"/>
+      <c r="M34" s="35"/>
       <c r="O34" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>beq   r4, r0, #9</v>
+        <f>CONCATENATE(IF(AND(ISBLANK($K34),ISBLANK($L34),ISBLANK($M34)),$J34,CONCATENATE($J34,IF(LEN($J34)=2,"    ",IF(LEN($J34)=3,"   ","  ")))),IF(OR(AND(ISBLANK($L34),ISBLANK($M34)),ISBLANK($K34)),$K34,CONCATENATE($K34,", ")),IF(OR(ISBLANK($M34),ISBLANK($L34)),$L34,CONCATENATE($L34,", ")),IF(ISBLANK($M34),"",CONCATENATE("#",$M34)))</f>
+        <v>nop</v>
       </c>
       <c r="Q34" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>22009</v>
+        <f>DEC2HEX(IF(ISBLANK($J34),0,(VLOOKUP($J34,$A$2:$C$24,2,FALSE)*16384))+IF(ISBLANK($K34),0,(VLOOKUP($K34,$A$26:$B$33,2,FALSE)*2048))+IF(ISBLANK($L34),0,(VLOOKUP($L34,$A$26:$B$33,2,FALSE)*256))+HEX2DEC($M34)+IF(ISBLANK($J34),0,VLOOKUP($J34,$A$2:$C$24,3,FALSE)),5)</f>
+        <v>00000</v>
       </c>
       <c r="S34" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>2009</v>
+        <v>0000</v>
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.25">
@@ -2499,32 +2493,26 @@
       </c>
       <c r="I35" s="23"/>
       <c r="J35" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="K35" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="L35" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="M35" s="35" t="s">
-        <v>45</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K35" s="33"/>
+      <c r="L35" s="33"/>
+      <c r="M35" s="35"/>
       <c r="O35" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>beq   r4, r0, #3c</v>
+        <f>CONCATENATE(IF(AND(ISBLANK($K35),ISBLANK($L35),ISBLANK($M35)),$J35,CONCATENATE($J35,IF(LEN($J35)=2,"    ",IF(LEN($J35)=3,"   ","  ")))),IF(OR(AND(ISBLANK($L35),ISBLANK($M35)),ISBLANK($K35)),$K35,CONCATENATE($K35,", ")),IF(OR(ISBLANK($M35),ISBLANK($L35)),$L35,CONCATENATE($L35,", ")),IF(ISBLANK($M35),"",CONCATENATE("#",$M35)))</f>
+        <v>nop</v>
       </c>
       <c r="Q35" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>2203C</v>
+        <f>DEC2HEX(IF(ISBLANK($J35),0,(VLOOKUP($J35,$A$2:$C$24,2,FALSE)*16384))+IF(ISBLANK($K35),0,(VLOOKUP($K35,$A$26:$B$33,2,FALSE)*2048))+IF(ISBLANK($L35),0,(VLOOKUP($L35,$A$26:$B$33,2,FALSE)*256))+HEX2DEC($M35)+IF(ISBLANK($J35),0,VLOOKUP($J35,$A$2:$C$24,3,FALSE)),5)</f>
+        <v>00000</v>
       </c>
       <c r="R35" s="5" t="str">
         <f>TEXT(DEC2HEX((FLOOR(HEX2DEC($Q35)/65536,1)*4) + FLOOR(HEX2DEC($Q34)/65536,1)),"0")</f>
-        <v>A</v>
+        <v>0</v>
       </c>
       <c r="S35" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>203C</v>
+        <v>0000</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.25">
@@ -2545,20 +2533,20 @@
       <c r="L36" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="M36" s="36" t="s">
-        <v>47</v>
+      <c r="M36" s="36">
+        <v>9</v>
       </c>
       <c r="O36" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>beq   r4, r0, #dd</v>
+        <f>CONCATENATE(IF(AND(ISBLANK($K36),ISBLANK($L36),ISBLANK($M36)),$J36,CONCATENATE($J36,IF(LEN($J36)=2,"    ",IF(LEN($J36)=3,"   ","  ")))),IF(OR(AND(ISBLANK($L36),ISBLANK($M36)),ISBLANK($K36)),$K36,CONCATENATE($K36,", ")),IF(OR(ISBLANK($M36),ISBLANK($L36)),$L36,CONCATENATE($L36,", ")),IF(ISBLANK($M36),"",CONCATENATE("#",$M36)))</f>
+        <v>beq   r4, r0, #9</v>
       </c>
       <c r="Q36" s="5" t="str">
         <f>DEC2HEX(IF(ISBLANK($J36),0,(VLOOKUP($J36,$A$2:$C$24,2,FALSE)*16384))+IF(ISBLANK($K36),0,(VLOOKUP($K36,$A$26:$B$33,2,FALSE)*2048))+IF(ISBLANK($L36),0,(VLOOKUP($L36,$A$26:$B$33,2,FALSE)*256))+HEX2DEC($M36)+IF(ISBLANK($J36),0,VLOOKUP($J36,$A$2:$C$24,3,FALSE)),5)</f>
-        <v>220DD</v>
+        <v>22009</v>
       </c>
       <c r="S36" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>20DD</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
@@ -2577,11 +2565,11 @@
       <c r="L37" s="34"/>
       <c r="M37" s="35"/>
       <c r="O37" s="19" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE(IF(AND(ISBLANK($K37),ISBLANK($L37),ISBLANK($M37)),$J37,CONCATENATE($J37,IF(LEN($J37)=2,"    ",IF(LEN($J37)=3,"   ","  ")))),IF(OR(AND(ISBLANK($L37),ISBLANK($M37)),ISBLANK($K37)),$K37,CONCATENATE($K37,", ")),IF(OR(ISBLANK($M37),ISBLANK($L37)),$L37,CONCATENATE($L37,", ")),IF(ISBLANK($M37),"",CONCATENATE("#",$M37)))</f>
         <v>nop</v>
       </c>
       <c r="Q37" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f>DEC2HEX(IF(ISBLANK($J37),0,(VLOOKUP($J37,$A$2:$C$24,2,FALSE)*16384))+IF(ISBLANK($K37),0,(VLOOKUP($K37,$A$26:$B$33,2,FALSE)*2048))+IF(ISBLANK($L37),0,(VLOOKUP($L37,$A$26:$B$33,2,FALSE)*256))+HEX2DEC($M37)+IF(ISBLANK($J37),0,VLOOKUP($J37,$A$2:$C$24,3,FALSE)),5)</f>
         <v>00000</v>
       </c>
       <c r="R37" s="5" t="str">
@@ -2603,22 +2591,28 @@
       </c>
       <c r="I38" s="24"/>
       <c r="J38" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="K38" s="34"/>
-      <c r="L38" s="34"/>
-      <c r="M38" s="36"/>
+        <v>13</v>
+      </c>
+      <c r="K38" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="L38" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="M38" s="36" t="s">
+        <v>46</v>
+      </c>
       <c r="O38" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>nop</v>
+        <f>CONCATENATE(IF(AND(ISBLANK($K38),ISBLANK($L38),ISBLANK($M38)),$J38,CONCATENATE($J38,IF(LEN($J38)=2,"    ",IF(LEN($J38)=3,"   ","  ")))),IF(OR(AND(ISBLANK($L38),ISBLANK($M38)),ISBLANK($K38)),$K38,CONCATENATE($K38,", ")),IF(OR(ISBLANK($M38),ISBLANK($L38)),$L38,CONCATENATE($L38,", ")),IF(ISBLANK($M38),"",CONCATENATE("#",$M38)))</f>
+        <v>beq   r4, r0, #DD</v>
       </c>
       <c r="Q38" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>00000</v>
+        <f>DEC2HEX(IF(ISBLANK($J38),0,(VLOOKUP($J38,$A$2:$C$24,2,FALSE)*16384))+IF(ISBLANK($K38),0,(VLOOKUP($K38,$A$26:$B$33,2,FALSE)*2048))+IF(ISBLANK($L38),0,(VLOOKUP($L38,$A$26:$B$33,2,FALSE)*256))+HEX2DEC($M38)+IF(ISBLANK($J38),0,VLOOKUP($J38,$A$2:$C$24,3,FALSE)),5)</f>
+        <v>220DD</v>
       </c>
       <c r="S38" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>0000</v>
+        <v>20DD</v>
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.25">
@@ -2646,7 +2640,7 @@
       </c>
       <c r="R39" s="5" t="str">
         <f t="shared" ref="R39" si="19">TEXT(DEC2HEX((FLOOR(HEX2DEC($Q39)/65536,1)*4) + FLOOR(HEX2DEC($Q38)/65536,1)),"0")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S39" s="5" t="str">
         <f t="shared" si="2"/>
@@ -2912,7 +2906,7 @@
         <v>16</v>
       </c>
       <c r="M48" s="36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O48" s="19" t="str">
         <f t="shared" si="0"/>
@@ -2964,11 +2958,11 @@
       </c>
       <c r="U49" s="6" t="str">
         <f>CONCATENATE(".INIT_",$T49,"(256'h",$S49,"_",$S48,"_",$S47,"_",$S46,"_",$S45,"_",S44,"_",$S43,"_",$S42,"_",$S41,"_",$S40,"_",$S39,"_",$S38,"_",$S37,"_",$S36,"_",$S35,"_",$S34,"),")</f>
-        <v>.INIT_02(256'h0000_00E1_0000_0000_0000_0000_0000_0000_0000_0000_0000_0000_0000_20DD_203C_2009),</v>
+        <v>.INIT_02(256'h0000_00E1_0000_0000_0000_0000_0000_0000_0000_0000_0000_20DD_0000_2009_0000_0000),</v>
       </c>
       <c r="V49" t="str">
         <f>CONCATENATE($R49,$R47,$R45,$R43,$R41,$R39,$R37,$R35)</f>
-        <v>2000002A</v>
+        <v>20000220</v>
       </c>
     </row>
     <row r="50" spans="7:22" x14ac:dyDescent="0.25">
@@ -5278,7 +5272,7 @@
       </c>
       <c r="W129" s="6" t="str">
         <f>CONCATENATE(".INITP_",TEXT(DEC2HEX(ROUNDDOWN(HEX2DEC($T129)/8,2)),"00"),"(256'h",$V129,$V113,$V97,$V81,$V65,$V49,$V33,$V17,"),")</f>
-        <v>.INITP_00(256'h00000000000000000000000000000000000000002000002A0000000000050400),</v>
+        <v>.INITP_00(256'h0000000000000000000000000000000000000000200002200000000000050400),</v>
       </c>
     </row>
     <row r="130" spans="7:23" x14ac:dyDescent="0.25">
